--- a/output/pdf_financials_xlsx/AFX.xlsx
+++ b/output/pdf_financials_xlsx/AFX.xlsx
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>2.891</v>
+        <v>2.884766</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.773088</v>
+        <v>0.145913</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.30453</v>
+        <v>0.210309</v>
       </c>
     </row>
     <row r="119">
@@ -3885,7 +3885,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>-0.006234</v>
       </c>

--- a/output/pdf_financials_xlsx/AFX.xlsx
+++ b/output/pdf_financials_xlsx/AFX.xlsx
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.337532</v>
+        <v>1.402942</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.097552</v>
+        <v>0.538013</v>
       </c>
     </row>
     <row r="11">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.337532</v>
+        <v>-1.402942</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.097552</v>
+        <v>-0.538013</v>
       </c>
     </row>
     <row r="12">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.474476</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.032322</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000131</v>
       </c>
     </row>
     <row r="35">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.474476</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.032322</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000131</v>
       </c>
     </row>
     <row r="37">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.6941850000000001</v>
+        <v>0.219709</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.070197</v>
+        <v>0.037875</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.030131</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="49">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3220,7 +3220,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.0125</v>
       </c>
@@ -3916,7 +3920,11 @@
           <t>Refund on reclamation deposit</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -4441,7 +4449,11 @@
           <t>Refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -4856,7 +4868,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4982,7 +4994,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5903,7 +5915,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/AFX.xlsx
+++ b/output/pdf_financials_xlsx/AFX.xlsx
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020907</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.009624000000000001</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.016277</v>
       </c>
     </row>
     <row r="102">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.011331</v>
+        <v>-0.032238</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.277948</v>
+        <v>0.287572</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.08502999999999999</v>
+        <v>0.101307</v>
       </c>
     </row>
     <row r="107">
@@ -3769,7 +3769,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.020907</v>
       </c>
